--- a/4. Supervised Learning (modeling and evaluation)/biases_layer2.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/biases_layer2.xlsx
@@ -435,502 +435,502 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.1573055600892571</v>
+        <v>0.02773583453878572</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.06978178204697033</v>
+        <v>0.1032589463417255</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.138946479153509</v>
+        <v>-0.09907632332353337</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.09283162622100974</v>
+        <v>-0.1773952891349706</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.09154434252043742</v>
+        <v>0.02027797410166655</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.004575792025808495</v>
+        <v>0.1298326592614745</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.08693720782533076</v>
+        <v>-0.02306746375983679</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.147153507079982</v>
+        <v>-0.127973545438893</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.03939673657572085</v>
+        <v>-0.1535444065794955</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.1133018464509841</v>
+        <v>0.08294848609029949</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.06555811605788905</v>
+        <v>-0.1467836566585176</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.04281557735854469</v>
+        <v>0.03267164835251898</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.09689466624792495</v>
+        <v>0.1152506397769515</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.06138133490181472</v>
+        <v>-0.04732392024048051</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.06077269646941491</v>
+        <v>0.1031294303191992</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.08518020608353614</v>
+        <v>0.07081130326306545</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.02745537710932818</v>
+        <v>0.06946189669480381</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-0.03333436195380768</v>
+        <v>-0.07258676191850182</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.008316170552111375</v>
+        <v>0.109690107143365</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.06578139346743159</v>
+        <v>0.06662616886849947</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-0.08980749364960984</v>
+        <v>0.03202183245903559</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-0.1558046296746904</v>
+        <v>-0.06394659143834662</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.1063010620064291</v>
+        <v>-0.001584808907623569</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-0.008860779942966598</v>
+        <v>-0.0639977472729803</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-0.1235570684231965</v>
+        <v>0.01019158384172095</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.03440501806837926</v>
+        <v>0.01947414529259347</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.1320433079651794</v>
+        <v>-0.141134765238094</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-0.09600533614625048</v>
+        <v>0.154844574631774</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.07694667240846106</v>
+        <v>0.01838073937582807</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.1482777136371539</v>
+        <v>-0.1330266230503571</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.004014385095824718</v>
+        <v>-0.1371916062446096</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.01151394906411169</v>
+        <v>-0.1616618907577225</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-0.08710125127904245</v>
+        <v>-0.1134613076998074</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.0215366488994877</v>
+        <v>-0.08668379532443626</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-0.0664312873474069</v>
+        <v>0.07211056569494595</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-0.01779787049163097</v>
+        <v>-0.1323695169055102</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.088342734475746</v>
+        <v>0.07377619673183246</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.0952435579456548</v>
+        <v>0.03085211342568184</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.1286999767972994</v>
+        <v>0.163822940946081</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-0.1398502491076555</v>
+        <v>-0.1672117728654922</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.09271551413757349</v>
+        <v>0.09434249351666825</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.1655291731622198</v>
+        <v>0.1483091162494584</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-0.1199783750511126</v>
+        <v>0.14325702584713</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-0.05839210859874524</v>
+        <v>-0.06500537939696831</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-0.06134876164634087</v>
+        <v>-0.05601947041654375</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-0.1281019852564165</v>
+        <v>-0.01565087040872584</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.01167962652510282</v>
+        <v>0.01045901285254638</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-0.02036390058672774</v>
+        <v>0.01715660739897071</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-0.1711826948377154</v>
+        <v>-0.1320838393298003</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.05029880864496845</v>
+        <v>0.03352984861783614</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.08158797724011896</v>
+        <v>-0.07289720182047804</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-0.1179825744672529</v>
+        <v>0.03406768873490561</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.0319581577736552</v>
+        <v>0.1633936015868697</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.1043225379174887</v>
+        <v>-0.05207804421474797</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.05072794354416099</v>
+        <v>0.0818056242905417</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-0.116097014500619</v>
+        <v>0.07093828795703705</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-0.1381467860385889</v>
+        <v>0.1637898246725203</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-0.05868894433877677</v>
+        <v>0.1831710903243216</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.06759695011638051</v>
+        <v>-0.1733998547424476</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-0.1474428294227576</v>
+        <v>0.04581809232875214</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-0.08795242374259693</v>
+        <v>-0.04383758316583237</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.02948193180848814</v>
+        <v>0.1176505193260102</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-0.1245576796051689</v>
+        <v>0.1495859232561128</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-0.05054302857092467</v>
+        <v>-0.160862073473794</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.1342293101950421</v>
+        <v>0.1543881048181262</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-0.09469566811077407</v>
+        <v>0.004579642570483915</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.01738343028640283</v>
+        <v>-0.1223108919613796</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.001306763964650065</v>
+        <v>-0.07335009234174648</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.07431689333076921</v>
+        <v>-0.09222098560927741</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-0.1128974504772429</v>
+        <v>-0.02607010723562543</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.1352220968662126</v>
+        <v>0.1629945499079187</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.01903015600512113</v>
+        <v>-0.07586459941148639</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.09855510244695989</v>
+        <v>-0.09048111714419652</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.07619757611676942</v>
+        <v>-0.08368937470198645</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-0.1226848189634523</v>
+        <v>0.0942032664833206</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.01527055750000621</v>
+        <v>0.02455763733695923</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-0.01191322220420966</v>
+        <v>-0.1499647253155672</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.05071088457087597</v>
+        <v>0.08081055012043038</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.1597821083016994</v>
+        <v>-0.1572968367959815</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.07599578833205954</v>
+        <v>0.05120975201942757</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-0.02512049838796488</v>
+        <v>0.01430800832111833</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.006850421521901295</v>
+        <v>0.06150556631883113</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.1766506455613723</v>
+        <v>0.1656321841387111</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-0.08367228791060256</v>
+        <v>-0.1025570443931885</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.05245869558472951</v>
+        <v>-0.06864902352374538</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.1373827126694036</v>
+        <v>0.1209813762914474</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-0.1762646777998781</v>
+        <v>0.02156728317316386</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-0.01715876639703684</v>
+        <v>0.01145376420961861</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-0.108412609403749</v>
+        <v>-0.1326393401386238</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-0.00709259456643536</v>
+        <v>-0.1309878517323393</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.03073092843958279</v>
+        <v>0.1287416552849382</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.1654994640429073</v>
+        <v>-0.06914969635147564</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.1335617912181592</v>
+        <v>-0.1278863386164183</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.1155992489388385</v>
+        <v>0.14661866671149</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.03066244703367643</v>
+        <v>-0.1090743287862958</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.05330807343369039</v>
+        <v>0.1161317783264881</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.04283376702594711</v>
+        <v>0.01773637796060156</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.06746126844476584</v>
+        <v>-0.05469163355897402</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-0.1578441123333693</v>
+        <v>-0.01286348460294422</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.01086432713540951</v>
+        <v>0.1599389922337096</v>
       </c>
     </row>
   </sheetData>

--- a/4. Supervised Learning (modeling and evaluation)/biases_layer2.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/biases_layer2.xlsx
@@ -435,502 +435,502 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02773583453878572</v>
+        <v>-0.01985561817300045</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.1032589463417255</v>
+        <v>-0.1539424695184785</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.09907632332353337</v>
+        <v>0.03585443301089638</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.1773952891349706</v>
+        <v>0.001037604841947354</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.02027797410166655</v>
+        <v>0.01587812265488819</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1298326592614745</v>
+        <v>0.1185568754749492</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.02306746375983679</v>
+        <v>-0.1339325361850011</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.127973545438893</v>
+        <v>-0.09293670383199672</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.1535444065794955</v>
+        <v>-0.003413498426561773</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.08294848609029949</v>
+        <v>-0.02529803144764219</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.1467836566585176</v>
+        <v>-0.05110245708464552</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.03267164835251898</v>
+        <v>-0.05775616292909973</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.1152506397769515</v>
+        <v>0.1693801694825371</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.04732392024048051</v>
+        <v>-0.1132575684318904</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.1031294303191992</v>
+        <v>0.1060093547428562</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.07081130326306545</v>
+        <v>-0.08251043326856511</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.06946189669480381</v>
+        <v>0.1810011599984975</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-0.07258676191850182</v>
+        <v>0.1621656818716581</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.109690107143365</v>
+        <v>0.1082591236044887</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.06662616886849947</v>
+        <v>-0.1357009163979346</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.03202183245903559</v>
+        <v>0.1236246568523189</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-0.06394659143834662</v>
+        <v>0.1066504001906916</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-0.001584808907623569</v>
+        <v>0.1035245371875164</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-0.0639977472729803</v>
+        <v>0.04079490813058623</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.01019158384172095</v>
+        <v>-0.04966468141552162</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.01947414529259347</v>
+        <v>0.0727205583504294</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-0.141134765238094</v>
+        <v>0.099976428588402</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.154844574631774</v>
+        <v>0.1006858848249501</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.01838073937582807</v>
+        <v>-0.06473578930898553</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0.1330266230503571</v>
+        <v>-0.1813987617872095</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-0.1371916062446096</v>
+        <v>-0.06013755230852863</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-0.1616618907577225</v>
+        <v>-0.1490577187681619</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-0.1134613076998074</v>
+        <v>0.1129146445159169</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0.08668379532443626</v>
+        <v>0.05276970570063705</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.07211056569494595</v>
+        <v>-0.1559480044950725</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-0.1323695169055102</v>
+        <v>0.009244763744263751</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.07377619673183246</v>
+        <v>0.1517051470148798</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.03085211342568184</v>
+        <v>-0.1356619708610134</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.163822940946081</v>
+        <v>0.03883839119715374</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-0.1672117728654922</v>
+        <v>0.1543524456511137</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.09434249351666825</v>
+        <v>-0.08448528503985098</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.1483091162494584</v>
+        <v>-0.1303705712792972</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.14325702584713</v>
+        <v>0.1267719291014621</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-0.06500537939696831</v>
+        <v>0.1689952560660983</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-0.05601947041654375</v>
+        <v>-0.1499292042445014</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-0.01565087040872584</v>
+        <v>0.04729426569048328</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.01045901285254638</v>
+        <v>0.1166854649344581</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.01715660739897071</v>
+        <v>0.04158359401473805</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-0.1320838393298003</v>
+        <v>-0.0238806491696166</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.03352984861783614</v>
+        <v>0.1575504009000221</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-0.07289720182047804</v>
+        <v>0.07436867766385503</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.03406768873490561</v>
+        <v>-0.1313512584456208</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.1633936015868697</v>
+        <v>-0.1637534637428111</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-0.05207804421474797</v>
+        <v>-0.1556633693197921</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.0818056242905417</v>
+        <v>-0.1579941329876015</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.07093828795703705</v>
+        <v>-0.1046932462037311</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.1637898246725203</v>
+        <v>0.1642507179422326</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.1831710903243216</v>
+        <v>-0.09718517219838865</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-0.1733998547424476</v>
+        <v>-0.03343645500014242</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.04581809232875214</v>
+        <v>0.163245449918031</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-0.04383758316583237</v>
+        <v>-0.04587642774219562</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.1176505193260102</v>
+        <v>0.1235976397574631</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.1495859232561128</v>
+        <v>-0.0993705048692043</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-0.160862073473794</v>
+        <v>0.1633840120934021</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.1543881048181262</v>
+        <v>-0.1384416463695338</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.004579642570483915</v>
+        <v>-0.02476146623738237</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-0.1223108919613796</v>
+        <v>0.0690651443845732</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-0.07335009234174648</v>
+        <v>-0.1298456404708884</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-0.09222098560927741</v>
+        <v>0.1199334104754363</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-0.02607010723562543</v>
+        <v>0.0629104417552952</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.1629945499079187</v>
+        <v>0.05940185145236013</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-0.07586459941148639</v>
+        <v>-0.1193273908403437</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-0.09048111714419652</v>
+        <v>-0.02432380402285102</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-0.08368937470198645</v>
+        <v>-0.1420065596896632</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.0942032664833206</v>
+        <v>-0.1033674089238893</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.02455763733695923</v>
+        <v>-0.07948191075882864</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-0.1499647253155672</v>
+        <v>-0.006068197331076702</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.08081055012043038</v>
+        <v>-0.1771193162599336</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-0.1572968367959815</v>
+        <v>-0.1664123801994802</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.05120975201942757</v>
+        <v>0.07785856638360986</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.01430800832111833</v>
+        <v>-0.06751965037312267</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.06150556631883113</v>
+        <v>-0.1436452377814714</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.1656321841387111</v>
+        <v>-0.005185505230547776</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-0.1025570443931885</v>
+        <v>0.1371199149125298</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-0.06864902352374538</v>
+        <v>-0.1246238579941306</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.1209813762914474</v>
+        <v>0.06005022225492915</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.02156728317316386</v>
+        <v>-0.004798419318025422</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.01145376420961861</v>
+        <v>0.09799107060326699</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-0.1326393401386238</v>
+        <v>-0.1403109680152761</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-0.1309878517323393</v>
+        <v>-0.1381450198613225</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.1287416552849382</v>
+        <v>0.0811208608433559</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-0.06914969635147564</v>
+        <v>-0.1345611380989655</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-0.1278863386164183</v>
+        <v>-0.05493270309188004</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.14661866671149</v>
+        <v>0.07699103280091239</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-0.1090743287862958</v>
+        <v>0.06295401117529936</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.1161317783264881</v>
+        <v>-0.1745723674710696</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.01773637796060156</v>
+        <v>-0.02635221321282286</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-0.05469163355897402</v>
+        <v>0.02744641568845119</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-0.01286348460294422</v>
+        <v>-0.08772265155242924</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.1599389922337096</v>
+        <v>-0.1081579822929194</v>
       </c>
     </row>
   </sheetData>

--- a/4. Supervised Learning (modeling and evaluation)/biases_layer2.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/biases_layer2.xlsx
@@ -435,502 +435,502 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.01985561817300045</v>
+        <v>0.03294799854271225</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.1539424695184785</v>
+        <v>-0.1191554604630769</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.03585443301089638</v>
+        <v>-0.06692297754783777</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.001037604841947354</v>
+        <v>0.1654985721341719</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.01587812265488819</v>
+        <v>-0.146025443002873</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1185568754749492</v>
+        <v>-0.0266200125475893</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.1339325361850011</v>
+        <v>-0.02868643002423429</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.09293670383199672</v>
+        <v>0.07009060381768548</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.003413498426561773</v>
+        <v>-0.1370661191991786</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.02529803144764219</v>
+        <v>0.08834061636854579</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.05110245708464552</v>
+        <v>-0.0175133431923652</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.05775616292909973</v>
+        <v>0.1391777461285243</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.1693801694825371</v>
+        <v>0.1280141370399696</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.1132575684318904</v>
+        <v>0.1269644000064909</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.1060093547428562</v>
+        <v>-0.01360862447263377</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.08251043326856511</v>
+        <v>0.02238476286545012</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.1810011599984975</v>
+        <v>-0.04005769788852889</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.1621656818716581</v>
+        <v>0.008568690720712592</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.1082591236044887</v>
+        <v>-0.004382754925978995</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0.1357009163979346</v>
+        <v>0.1152860093177414</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.1236246568523189</v>
+        <v>0.01902213228104101</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.1066504001906916</v>
+        <v>-0.006172036371287576</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.1035245371875164</v>
+        <v>-0.03100163129090358</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.04079490813058623</v>
+        <v>0.1288774605791042</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-0.04966468141552162</v>
+        <v>-0.04863096894751995</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.0727205583504294</v>
+        <v>0.1233973117363214</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.099976428588402</v>
+        <v>0.1573229321453289</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.1006858848249501</v>
+        <v>0.03765198287913218</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-0.06473578930898553</v>
+        <v>0.1055184679649685</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0.1813987617872095</v>
+        <v>-0.05282123241664451</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-0.06013755230852863</v>
+        <v>0.1523789846711696</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-0.1490577187681619</v>
+        <v>0.01906019237678921</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.1129146445159169</v>
+        <v>0.1640130361414431</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.05276970570063705</v>
+        <v>-0.04621284439440554</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-0.1559480044950725</v>
+        <v>0.07813235475567766</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.009244763744263751</v>
+        <v>0.02027655522252697</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.1517051470148798</v>
+        <v>0.05154752906638246</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-0.1356619708610134</v>
+        <v>0.02235502950564864</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.03883839119715374</v>
+        <v>0.07256452183434764</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.1543524456511137</v>
+        <v>-0.04563652091126091</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-0.08448528503985098</v>
+        <v>0.1171430593867862</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-0.1303705712792972</v>
+        <v>-0.0985118709135633</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.1267719291014621</v>
+        <v>0.1150780019238463</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.1689952560660983</v>
+        <v>0.02989901339012416</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-0.1499292042445014</v>
+        <v>-0.1046617620271624</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.04729426569048328</v>
+        <v>-0.0752973900233161</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.1166854649344581</v>
+        <v>0.1103904396935756</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.04158359401473805</v>
+        <v>0.1147699742484139</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-0.0238806491696166</v>
+        <v>-0.05819339588246747</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.1575504009000221</v>
+        <v>-0.1346205388773906</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.07436867766385503</v>
+        <v>-0.151929122498048</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-0.1313512584456208</v>
+        <v>-0.1576611164006419</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-0.1637534637428111</v>
+        <v>0.1211930937405607</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-0.1556633693197921</v>
+        <v>0.02425198892676706</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-0.1579941329876015</v>
+        <v>0.05353229909423054</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-0.1046932462037311</v>
+        <v>-0.1521326902016474</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.1642507179422326</v>
+        <v>-0.1273877367066079</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-0.09718517219838865</v>
+        <v>0.1347885216615809</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-0.03343645500014242</v>
+        <v>-0.06436210571661076</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.163245449918031</v>
+        <v>0.1263252665036092</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-0.04587642774219562</v>
+        <v>-0.01182774535535761</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.1235976397574631</v>
+        <v>0.1534077575486453</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-0.0993705048692043</v>
+        <v>0.1677262779791538</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.1633840120934021</v>
+        <v>0.05006735280759</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-0.1384416463695338</v>
+        <v>-0.106765883408529</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-0.02476146623738237</v>
+        <v>0.07721597207890027</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.0690651443845732</v>
+        <v>-0.08414708953538556</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-0.1298456404708884</v>
+        <v>-0.02119313598726077</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.1199334104754363</v>
+        <v>0.1363727669452778</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.0629104417552952</v>
+        <v>-0.04621587982063423</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.05940185145236013</v>
+        <v>-0.1522243554140306</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-0.1193273908403437</v>
+        <v>-0.13470107678123</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-0.02432380402285102</v>
+        <v>-0.08566621726611791</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-0.1420065596896632</v>
+        <v>-0.0878671603852719</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-0.1033674089238893</v>
+        <v>-0.002252159104834523</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-0.07948191075882864</v>
+        <v>0.02289988621725477</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-0.006068197331076702</v>
+        <v>0.08363993472226357</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-0.1771193162599336</v>
+        <v>-0.07521456740754237</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-0.1664123801994802</v>
+        <v>0.04486791601938862</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.07785856638360986</v>
+        <v>0.09364848782169038</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-0.06751965037312267</v>
+        <v>-0.002686752694958736</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-0.1436452377814714</v>
+        <v>0.180776538780082</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-0.005185505230547776</v>
+        <v>-0.1560353218566833</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.1371199149125298</v>
+        <v>0.1115859534901909</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-0.1246238579941306</v>
+        <v>0.06726185425302927</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.06005022225492915</v>
+        <v>0.1328984600603971</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-0.004798419318025422</v>
+        <v>0.157809032487354</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.09799107060326699</v>
+        <v>0.05333988752893221</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-0.1403109680152761</v>
+        <v>-0.01849521827926038</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-0.1381450198613225</v>
+        <v>-0.09281096277196285</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.0811208608433559</v>
+        <v>-0.03636206268200785</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-0.1345611380989655</v>
+        <v>-0.1683202440301151</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-0.05493270309188004</v>
+        <v>0.1180990592696718</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.07699103280091239</v>
+        <v>0.1168201583341046</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.06295401117529936</v>
+        <v>0.05710073491343368</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-0.1745723674710696</v>
+        <v>-0.09839846082369802</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-0.02635221321282286</v>
+        <v>-0.0475343674501008</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.02744641568845119</v>
+        <v>-0.08308543791214595</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-0.08772265155242924</v>
+        <v>-0.1429424092751725</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-0.1081579822929194</v>
+        <v>0.1563222846761412</v>
       </c>
     </row>
   </sheetData>

--- a/4. Supervised Learning (modeling and evaluation)/biases_layer2.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/biases_layer2.xlsx
@@ -435,502 +435,502 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03294799854271225</v>
+        <v>-0.05768061869363202</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.1191554604630769</v>
+        <v>0.01631223036328101</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.06692297754783777</v>
+        <v>0.1601078379252359</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.1654985721341719</v>
+        <v>-0.004292170471654282</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.146025443002873</v>
+        <v>-0.1698158866904156</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.0266200125475893</v>
+        <v>-0.1059718296081833</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.02868643002423429</v>
+        <v>-0.08462268451668212</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.07009060381768548</v>
+        <v>-0.01151863230082434</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.1370661191991786</v>
+        <v>0.1633455108879262</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.08834061636854579</v>
+        <v>-0.04941546206717072</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.0175133431923652</v>
+        <v>0.1166096077011469</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.1391777461285243</v>
+        <v>-0.1066605805573901</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.1280141370399696</v>
+        <v>0.0009930668275841225</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.1269644000064909</v>
+        <v>-0.1214809047663973</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0.01360862447263377</v>
+        <v>-0.01733533221357222</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.02238476286545012</v>
+        <v>0.1308398351106722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0.04005769788852889</v>
+        <v>0.1180743846202023</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.008568690720712592</v>
+        <v>0.0456786617008206</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0.004382754925978995</v>
+        <v>0.1219503724325452</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.1152860093177414</v>
+        <v>0.113430791353429</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.01902213228104101</v>
+        <v>0.03624825655268595</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-0.006172036371287576</v>
+        <v>-0.004619436593517939</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-0.03100163129090358</v>
+        <v>-0.1008753104067015</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.1288774605791042</v>
+        <v>-0.02134238496047627</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-0.04863096894751995</v>
+        <v>0.06117213479011466</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.1233973117363214</v>
+        <v>-0.1376061800378467</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.1573229321453289</v>
+        <v>0.1578695250854738</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.03765198287913218</v>
+        <v>0.05537745464506883</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.1055184679649685</v>
+        <v>0.1311736749843821</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0.05282123241664451</v>
+        <v>0.07402479427473467</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.1523789846711696</v>
+        <v>-0.1372587129398036</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.01906019237678921</v>
+        <v>-0.1050317879867836</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.1640130361414431</v>
+        <v>0.1046291519144284</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0.04621284439440554</v>
+        <v>-0.08754581675495636</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.07813235475567766</v>
+        <v>0.08458267996948128</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.02027655522252697</v>
+        <v>0.01696379935659509</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.05154752906638246</v>
+        <v>-0.058233148611783</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.02235502950564864</v>
+        <v>-0.00438120920171311</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.07256452183434764</v>
+        <v>-0.08905101673550601</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-0.04563652091126091</v>
+        <v>0.1417227242104753</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.1171430593867862</v>
+        <v>-0.07354662478400327</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-0.0985118709135633</v>
+        <v>-0.1579092530654064</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.1150780019238463</v>
+        <v>-0.08264806069437303</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.02989901339012416</v>
+        <v>0.07520878407246352</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-0.1046617620271624</v>
+        <v>-0.1631048209772335</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-0.0752973900233161</v>
+        <v>-0.02667483320831253</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.1103904396935756</v>
+        <v>-0.02487323928554766</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.1147699742484139</v>
+        <v>0.1301323983601839</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-0.05819339588246747</v>
+        <v>0.07769274978890787</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-0.1346205388773906</v>
+        <v>0.02213181590396622</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-0.151929122498048</v>
+        <v>0.04070231773399331</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-0.1576611164006419</v>
+        <v>-0.01676461018413858</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.1211930937405607</v>
+        <v>0.007572759726191791</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.02425198892676706</v>
+        <v>-0.02530405519069066</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.05353229909423054</v>
+        <v>0.1572856117772835</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-0.1521326902016474</v>
+        <v>-0.09089310997496808</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-0.1273877367066079</v>
+        <v>-0.1258247363099035</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.1347885216615809</v>
+        <v>-0.09311409622676466</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-0.06436210571661076</v>
+        <v>-0.1505159353287557</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.1263252665036092</v>
+        <v>-0.1423571026662598</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-0.01182774535535761</v>
+        <v>0.08505810447012979</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.1534077575486453</v>
+        <v>-0.1491359829482092</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.1677262779791538</v>
+        <v>0.158459435775751</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.05006735280759</v>
+        <v>0.03595253497244567</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-0.106765883408529</v>
+        <v>0.01002097389245265</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.07721597207890027</v>
+        <v>0.06473255979531516</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-0.08414708953538556</v>
+        <v>-0.1543437959006924</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-0.02119313598726077</v>
+        <v>-0.1565869003754287</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.1363727669452778</v>
+        <v>-0.09030924328187456</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-0.04621587982063423</v>
+        <v>0.06008097170303415</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-0.1522243554140306</v>
+        <v>0.05084294444601414</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-0.13470107678123</v>
+        <v>0.07995306078556268</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-0.08566621726611791</v>
+        <v>-0.01592544091550471</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-0.0878671603852719</v>
+        <v>0.1727436608778307</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-0.002252159104834523</v>
+        <v>-0.0936892172872351</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.02289988621725477</v>
+        <v>0.07691386666404229</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.08363993472226357</v>
+        <v>0.07400946626704882</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-0.07521456740754237</v>
+        <v>0.02753985263576621</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.04486791601938862</v>
+        <v>0.02013260456852567</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.09364848782169038</v>
+        <v>0.1169319557047207</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-0.002686752694958736</v>
+        <v>0.02405967630278949</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.180776538780082</v>
+        <v>-0.1281298514859859</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-0.1560353218566833</v>
+        <v>0.04217654344862813</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.1115859534901909</v>
+        <v>0.03471367428490188</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.06726185425302927</v>
+        <v>-0.1206181852218002</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.1328984600603971</v>
+        <v>-0.1627731229021727</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.157809032487354</v>
+        <v>0.04426463302510612</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.05333988752893221</v>
+        <v>0.07115538568683802</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-0.01849521827926038</v>
+        <v>-0.1285602739919154</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-0.09281096277196285</v>
+        <v>-0.03098761848438275</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-0.03636206268200785</v>
+        <v>0.1245667209256358</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-0.1683202440301151</v>
+        <v>0.1451141874989487</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.1180990592696718</v>
+        <v>-0.08987323716086398</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.1168201583341046</v>
+        <v>0.1379075548798321</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.05710073491343368</v>
+        <v>-0.1532068385746931</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-0.09839846082369802</v>
+        <v>-0.05664638753352498</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-0.0475343674501008</v>
+        <v>0.1519888635338905</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-0.08308543791214595</v>
+        <v>-0.122932458570143</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-0.1429424092751725</v>
+        <v>-0.06856341914355864</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.1563222846761412</v>
+        <v>0.09051056358523091</v>
       </c>
     </row>
   </sheetData>
